--- a/StructureDefinition-Analysutrustning-Resurs.xlsx
+++ b/StructureDefinition-Analysutrustning-Resurs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Analysutrustning-Resurs.xlsx
+++ b/StructureDefinition-Analysutrustning-Resurs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Analysutrustning : Resurs).</t>
+    <t>Klassen Analysutrustning håller information om den utrustning som använts för att utföra en analys.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -263,6 +263,9 @@
     <t>Source attribute: id; renamed from reserved FSH name 'id'</t>
   </si>
   <si>
+    <t>Identitetsbeteckning för en analysutrustning.Id identifierar unikt en viss instans av utrustning,till skillnad från attributet typ som identifierar en typ eller modellbeteckning.</t>
+  </si>
+  <si>
     <t>Analysutrustning-Resurs.typ</t>
   </si>
   <si>
@@ -271,6 +274,10 @@
   </si>
   <si>
     <t>Source attribute: typ</t>
+  </si>
+  <si>
+    <t>Typ eller modellbeteckning
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
   </si>
   <si>
     <t>Analysutrustning-Resurs.beskrivning</t>
@@ -876,7 +883,7 @@
         <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -944,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -970,13 +977,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1027,7 +1034,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
@@ -1044,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1070,14 +1077,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>87</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1127,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1144,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1170,13 +1175,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1227,7 +1232,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
